--- a/data/processed/positivacao/2026-03_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-03_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27597,7 +27597,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr"/>
@@ -38455,7 +38455,7 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr"/>
@@ -66697,7 +66697,7 @@
     <row r="2554">
       <c r="A2554" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2554" t="inlineStr"/>
@@ -68264,12 +68264,12 @@
       <c r="A2615" t="inlineStr"/>
       <c r="B2615" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 4 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 3.268,42
+          <t>Vendedor 1 - VENDEDOR 01: positivou 4 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 3.268,42
 Vendedor 18 - LOJA: positivou 339 cliente(s), não positivou 613 cliente(s) - Total vendido: R$ 126.340,13
-Vendedor 3 - FERNANDA: positivou 114 cliente(s), não positivou 303 cliente(s) - Total vendido: R$ 158.904,27
-Vendedor 4 - DANIELA: positivou 151 cliente(s), não positivou 485 cliente(s) - Total vendido: R$ 85.971,11
+Vendedor 3 - VENDEDOR 03: positivou 114 cliente(s), não positivou 303 cliente(s) - Total vendido: R$ 158.904,27
+Vendedor 4 - VENDEDOR 04: positivou 151 cliente(s), não positivou 485 cliente(s) - Total vendido: R$ 85.971,11
 Vendedor 5 - SITE: positivou 5 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 392,21
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 59 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 59 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2615" t="inlineStr"/>
